--- a/Advance Excel/Workbook1.xlsx
+++ b/Advance Excel/Workbook1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>S.No.</t>
   </si>
@@ -45,6 +45,15 @@
   </si>
   <si>
     <t>OR</t>
+  </si>
+  <si>
+    <t>Admit Card</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Match</t>
   </si>
   <si>
     <t>Sagar</t>
@@ -1230,13 +1239,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="12.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1255,13 +1265,22 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>90</v>
@@ -1273,13 +1292,29 @@
         <f>AND(C2&gt;60,D2&gt;=350)</f>
         <v>1</v>
       </c>
+      <c r="F2" t="b">
+        <f>OR(C2&gt;60,D2&gt;=350)</f>
+        <v>1</v>
+      </c>
+      <c r="G2" t="str">
+        <f>IF(AND(C2&gt;60,D2&gt;=350),"Alligible","Not Alligible")</f>
+        <v>Alligible</v>
+      </c>
+      <c r="H2" t="str">
+        <f>INDEX(B2:B11,4)</f>
+        <v>Rashid</v>
+      </c>
+      <c r="I2">
+        <f>MATCH("Manish",B1:B11,0)</f>
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>45</v>
@@ -1291,13 +1326,21 @@
         <f t="shared" ref="E3:E11" si="0">AND(C3&gt;60,D3&gt;=350)</f>
         <v>0</v>
       </c>
+      <c r="F3" t="b">
+        <f t="shared" ref="F3:F11" si="1">OR(C3&gt;60,D3&gt;=350)</f>
+        <v>1</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G11" si="2">IF(AND(C3&gt;60,D3&gt;=350),"Alligible","Not Alligible")</f>
+        <v>Not Alligible</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>65</v>
@@ -1309,13 +1352,21 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="F4" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="2"/>
+        <v>Alligible</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>56</v>
@@ -1327,13 +1378,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="F5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Alligible</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>55</v>
@@ -1345,13 +1404,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="F6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Alligible</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>66</v>
@@ -1363,13 +1430,21 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="F7" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="2"/>
+        <v>Alligible</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>56</v>
@@ -1381,13 +1456,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="F8" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Alligible</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>75</v>
@@ -1399,13 +1482,21 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="F9" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="2"/>
+        <v>Alligible</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>67</v>
@@ -1417,13 +1508,21 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="F10" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="2"/>
+        <v>Alligible</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <v>66</v>
@@ -1434,6 +1533,14 @@
       <c r="E11" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="2"/>
+        <v>Alligible</v>
       </c>
     </row>
   </sheetData>
